--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-23T19:06:52.883Z</t>
+    <t>2026-04-23T19:16:23.767Z</t>
   </si>
   <si>
     <t>WorkSafeNB | WorkSafeNB</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero-carousel","columns-news","columns-news","columns-news","cards-feature","cards-feature","cards-feature","tabs-resources","columns-contact"]</t>
+    <t>["carousel-homepage","columns-news","columns-news","columns-news","cards-feature","cards-feature","cards-feature","tabs-resources","columns-contact"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-23T19:06:52.883Z</t>
+    <t>2026-04-23T19:33:39.334Z</t>
   </si>
   <si>
     <t>WorkSafeNB | WorkSafeNB</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-23T19:33:39.334Z</t>
+    <t>2026-04-23T19:57:10.589Z</t>
   </si>
   <si>
     <t>WorkSafeNB | WorkSafeNB</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,48 @@
     <t>url</t>
   </si>
   <si>
+    <t>employers.report.json</t>
+  </si>
+  <si>
+    <t>["nav-panel","nav-panel","nav-panel","nav-panel","nav-panel","columns-contact"]</t>
+  </si>
+  <si>
+    <t>employers</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>section-landing</t>
+  </si>
+  <si>
+    <t>2026-04-24T21:23:19.724Z</t>
+  </si>
+  <si>
+    <t>WorkSafeNB | Employers</t>
+  </si>
+  <si>
+    <t>https://www.worksafenb.ca/employers/</t>
+  </si>
+  <si>
+    <t>health-care.report.json</t>
+  </si>
+  <si>
+    <t>["announcements","cards-overlay","nav-panel","nav-panel","nav-panel","nav-panel","columns-contact"]</t>
+  </si>
+  <si>
+    <t>health-care</t>
+  </si>
+  <si>
+    <t>2026-04-24T21:23:10.819Z</t>
+  </si>
+  <si>
+    <t>WorkSafeNB | Health Care</t>
+  </si>
+  <si>
+    <t>https://www.worksafenb.ca/health-care/</t>
+  </si>
+  <si>
     <t>index.report.json</t>
   </si>
   <si>
@@ -46,19 +88,52 @@
     <t>index</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-23T19:57:10.589Z</t>
+    <t>2026-04-24T22:14:37.492Z</t>
   </si>
   <si>
     <t>WorkSafeNB | WorkSafeNB</t>
   </si>
   <si>
     <t>https://www.worksafenb.ca/</t>
+  </si>
+  <si>
+    <t>policy-and-legal.report.json</t>
+  </si>
+  <si>
+    <t>["nav-panel","nav-panel","nav-panel","nav-panel","columns-contact"]</t>
+  </si>
+  <si>
+    <t>policy-and-legal</t>
+  </si>
+  <si>
+    <t>2026-04-24T21:23:24.285Z</t>
+  </si>
+  <si>
+    <t>WorkSafeNB | Policy and Legal</t>
+  </si>
+  <si>
+    <t>https://www.worksafenb.ca/policy-and-legal/</t>
+  </si>
+  <si>
+    <t>workers.report.json</t>
+  </si>
+  <si>
+    <t>["cards-overlay","nav-panel","nav-panel","nav-panel","nav-panel","columns-contact"]</t>
+  </si>
+  <si>
+    <t>workers</t>
+  </si>
+  <si>
+    <t>2026-04-24T21:23:15.360Z</t>
+  </si>
+  <si>
+    <t>WorkSafeNB | Workers</t>
+  </si>
+  <si>
+    <t>https://www.worksafenb.ca/workers/</t>
   </si>
 </sst>
 </file>
@@ -447,16 +522,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="7" max="7" width="31" customWidth="1"/>
+    <col min="8" max="8" width="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -509,6 +584,110 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>section-landing</t>
   </si>
   <si>
-    <t>2026-04-24T21:23:19.724Z</t>
+    <t>2026-04-24T23:00:27.473Z</t>
   </si>
   <si>
     <t>WorkSafeNB | Employers</t>
@@ -70,7 +70,7 @@
     <t>health-care</t>
   </si>
   <si>
-    <t>2026-04-24T21:23:10.819Z</t>
+    <t>2026-04-24T23:00:17.452Z</t>
   </si>
   <si>
     <t>WorkSafeNB | Health Care</t>
@@ -91,7 +91,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-24T22:14:37.492Z</t>
+    <t>2026-04-24T23:01:02.846Z</t>
   </si>
   <si>
     <t>WorkSafeNB | WorkSafeNB</t>
@@ -109,7 +109,7 @@
     <t>policy-and-legal</t>
   </si>
   <si>
-    <t>2026-04-24T21:23:24.285Z</t>
+    <t>2026-04-24T23:00:32.246Z</t>
   </si>
   <si>
     <t>WorkSafeNB | Policy and Legal</t>
@@ -127,7 +127,7 @@
     <t>workers</t>
   </si>
   <si>
-    <t>2026-04-24T21:23:15.360Z</t>
+    <t>2026-04-24T23:00:22.071Z</t>
   </si>
   <si>
     <t>WorkSafeNB | Workers</t>
